--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_advertencias/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="BJ4" s="6" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="BJ5" s="6" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="BJ6" s="6" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="BJ7" s="6" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="BJ8" s="6" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="BJ9" s="6" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="BJ10" s="6" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="BJ11" s="6" t="n">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="AT12" s="6" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="BJ12" s="6" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="BJ13" s="6" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="BJ14" s="6" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="BJ15" s="6" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="BJ16" s="6" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="BJ17" s="6" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="BJ18" s="6" t="n">
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>45807</v>
+        <v>45808</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="BJ19" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="BJ20" s="6" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="BJ21" s="6" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="BJ22" s="6" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="BJ23" s="6" t="n">
-        <v>46016</v>
+        <v>46017</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="BJ24" s="6" t="n">
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="BJ25" s="6" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="BJ26" s="6" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="BJ27" s="6" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="BJ28" s="6" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="BJ29" s="6" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>45773</v>
+        <v>45774</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="S30" s="6" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="T30" s="5" t="n">
         <v>17</v>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="BJ30" s="6" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="BJ31" s="6" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="BJ32" s="6" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>46561</v>
+        <v>46562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="AT33" s="6" t="n">
-        <v>46407</v>
+        <v>46408</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="BJ33" s="6" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
